--- a/results/表3_温度.xlsx
+++ b/results/表3_温度.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -640,7 +640,7 @@
     <row r="1" ht="14.1" customHeight="1" s="4">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>时间\到药材中心的距离</t>
+          <t>时间/h\到药材中心的距离/cm</t>
         </is>
       </c>
       <c r="B1" s="2" t="n">
@@ -661,122 +661,122 @@
     </row>
     <row r="2" ht="14.1" customHeight="1" s="4">
       <c r="A2" s="1" t="n">
-        <v>1800</v>
+        <v>0.5</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>32.189</v>
+        <v>32.1892</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>32.382</v>
+        <v>32.3821</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>32.966</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>33.961</v>
+        <v>33.9608</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>35.392</v>
+        <v>35.4131</v>
       </c>
     </row>
     <row r="3" ht="14.1" customHeight="1" s="4">
       <c r="A3" s="1" t="n">
-        <v>3600</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40.382</v>
+        <v>40.3815</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>40.554</v>
+        <v>40.5536</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.06</v>
+        <v>41.0605</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>41.878</v>
+        <v>41.8782</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>42.981</v>
+        <v>42.9975</v>
       </c>
     </row>
     <row r="4" ht="14.1" customHeight="1" s="4">
       <c r="A4" s="1" t="n">
-        <v>5400</v>
+        <v>1.5</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>45.847</v>
+        <v>45.8467</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>45.935</v>
+        <v>45.9348</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>46.193</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.605</v>
+        <v>46.6051</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>47.133</v>
+        <v>47.1401</v>
       </c>
     </row>
     <row r="5" ht="14.1" customHeight="1" s="4">
       <c r="A5" s="1" t="n">
-        <v>7200</v>
+        <v>2</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>48.45</v>
+        <v>48.4502</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>48.488</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48.598</v>
+        <v>48.5984</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>48.774</v>
+        <v>48.7735</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>49</v>
+        <v>49.0034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>9000</v>
+        <v>2.5</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>49.467</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>49.479</v>
+        <v>49.4792</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>49.514</v>
+        <v>49.5136</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>49.565</v>
+        <v>49.5653</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>49.659</v>
+        <v>49.6607</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>10800</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>49.849</v>
+        <v>49.8495</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49.855</v>
+        <v>49.8553</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>49.875</v>
+        <v>49.8746</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>49.91</v>
+        <v>49.9101</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>49.966</v>
+        <v>49.9664</v>
       </c>
     </row>
   </sheetData>
